--- a/output/details/2026-05-24/preprocessed_data.xlsx
+++ b/output/details/2026-05-24/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46166</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1149694279698529</v>
+        <v>-0.119993258005714</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1495560278276881</v>
+        <v>-0.1390984739481506</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1493518872097806</v>
+        <v>-0.1388255721303887</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1183198609980055</v>
+        <v>0.003695674064609401</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001698182658118648</v>
+        <v>0.001694288983119201</v>
       </c>
       <c r="G2" t="n">
-        <v>1.943343770808998</v>
+        <v>2.503814187516318</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4411871926514717</v>
+        <v>-0.272321205228563</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
